--- a/Speciallægeloft/speciallægeloft_data/Region_Syd.xlsx
+++ b/Speciallægeloft/speciallægeloft_data/Region_Syd.xlsx
@@ -85,7 +85,7 @@
     <t>Datasæt 11 2025</t>
   </si>
   <si>
-    <t>Kørsel 15.4.2026 13.48.39</t>
+    <t>Kørsel 15.4.2026 14.35.20</t>
   </si>
   <si>
     <t>Gruppe: Region Syd</t>
